--- a/SQL_Projects/Pizza_Sales_Data_Analysis/2_Descriptive_Sales_Analysis/Assets/Descriptive_Sales_Analysis_Excel.xlsx
+++ b/SQL_Projects/Pizza_Sales_Data_Analysis/2_Descriptive_Sales_Analysis/Assets/Descriptive_Sales_Analysis_Excel.xlsx
@@ -39,36 +39,36 @@
     <sheet name="Top Years" sheetId="30" r:id="rId30"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Bottom 10 Names (C)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Bottom 10 Names (T S)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bottom 10 Pizza IDs (C)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Bottom 10 Pizza IDs (T S)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Bottom 10 Pizza Type IDs (C)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Bottom 10 Pizza Type IDs (T S)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Top 10 Dates (C (D A))'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Top 10 Dates (C)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Top 10 Dates (T S (D A))'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Top 10 Dates (T S)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Top 10 Names (C)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Top 10 Names (T S)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'Top 10 Order Hours (C (H A))'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Top 10 Order Hours (C)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Top 10 Order Hours (T S (H A))'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Top 10 Order Hours (T S)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Top 10 Order Times (C (T A))'!$A$3:$M$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Top 10 Order Times (C)'!$A$3:$M$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Top 10 Order Times (T S (T A))'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Top 10 Order Times (T S)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Top 10 Pizza IDs (C)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Top 10 Pizza IDs (T S)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Top 10 Pizza Type IDs (C)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Top 10 Pizza Type IDs (T S)'!$A$3:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Top Categories (T S)'!$A$3:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Top Days'!$A$3:$M$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Top Months'!$A$3:$M$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Top Quarters'!$A$3:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Top Sizes (T S)'!$A$3:$M$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'Top Years'!$A$3:$M$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Bottom 10 Names (C)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Bottom 10 Names (T S)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bottom 10 Pizza IDs (C)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Bottom 10 Pizza IDs (T S)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Bottom 10 Pizza Type IDs (C)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Bottom 10 Pizza Type IDs (T S)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Top 10 Dates (C (D A))'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Top 10 Dates (C)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Top 10 Dates (T S (D A))'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Top 10 Dates (T S)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Top 10 Names (C)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Top 10 Names (T S)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'Top 10 Order Hours (C (H A))'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Top 10 Order Hours (C)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Top 10 Order Hours (T S (H A))'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Top 10 Order Hours (T S)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Top 10 Order Times (C (T A))'!$A$3:$M$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Top 10 Order Times (C)'!$A$3:$M$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Top 10 Order Times (T S (T A))'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Top 10 Order Times (T S)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Top 10 Pizza IDs (C)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Top 10 Pizza IDs (T S)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Top 10 Pizza Type IDs (C)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Top 10 Pizza Type IDs (T S)'!$A$3:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Top Categories (T S)'!$A$3:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Top Days'!$A$3:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Top Months'!$A$3:$M$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Top Quarters'!$A$3:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Top Sizes (T S)'!$A$3:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'Top Years'!$A$3:$M$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2772,7 +2772,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -3365,7 +3365,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -3958,7 +3958,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -4551,7 +4551,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -4862,7 +4862,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M6"/>
+  <autoFilter ref="A3:M7"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -5220,7 +5220,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M7"/>
+  <autoFilter ref="A3:M8"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -5813,7 +5813,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -6406,7 +6406,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -6999,7 +6999,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -7592,7 +7592,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -8185,7 +8185,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -8778,7 +8778,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -9371,7 +9371,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -11750,7 +11750,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M50"/>
+  <autoFilter ref="A3:M51"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -14129,7 +14129,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M50"/>
+  <autoFilter ref="A3:M51"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -14722,7 +14722,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -15315,7 +15315,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -15908,7 +15908,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -16501,7 +16501,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -16953,7 +16953,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M9"/>
+  <autoFilter ref="A3:M10"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -17640,7 +17640,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M14"/>
+  <autoFilter ref="A3:M15"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -17950,7 +17950,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M6"/>
+  <autoFilter ref="A3:M7"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -18543,7 +18543,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -18713,7 +18713,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M3"/>
+  <autoFilter ref="A3:M4"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -19306,7 +19306,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -19899,7 +19899,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -20492,7 +20492,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -21085,7 +21085,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -21678,7 +21678,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -22271,7 +22271,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M12"/>
+  <autoFilter ref="A3:M13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>

--- a/SQL_Projects/Pizza_Sales_Data_Analysis/2_Descriptive_Sales_Analysis/Assets/Descriptive_Sales_Analysis_Excel.xlsx
+++ b/SQL_Projects/Pizza_Sales_Data_Analysis/2_Descriptive_Sales_Analysis/Assets/Descriptive_Sales_Analysis_Excel.xlsx
@@ -572,22 +572,22 @@
     <t>day</t>
   </si>
   <si>
-    <t>Friday</t>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
   </si>
   <si>
     <t>Thursday</t>
   </si>
   <si>
-    <t>Saturday</t>
+    <t>Friday</t>
   </si>
   <si>
-    <t>Wednesday</t>
-  </si>
-  <si>
-    <t>Tuesday</t>
-  </si>
-  <si>
-    <t>Monday</t>
+    <t>Saturday</t>
   </si>
   <si>
     <t>Sunday</t>
@@ -1330,13 +1330,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0B713B"/>
+        <fgColor rgb="FFEDF8B2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEDF8B2"/>
+        <fgColor rgb="FF0B713B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1820,10 +1820,10 @@
     <xf numFmtId="0" fontId="3" fillId="89" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="90" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="90" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="91" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="91" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="92" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -16593,10 +16593,10 @@
         <v>165</v>
       </c>
       <c r="C4" s="5">
-        <v>8242</v>
-      </c>
-      <c r="D4" s="20">
-        <v>1</v>
+        <v>6485</v>
+      </c>
+      <c r="D4" s="51">
+        <v>6</v>
       </c>
       <c r="E4" s="7">
         <f>C4/SUM($C$4:$C$10)</f>
@@ -16611,13 +16611,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="9">
-        <v>16.78681223784851</v>
+        <v>16.85186842518449</v>
       </c>
       <c r="I4" s="10">
-        <v>136073.9</v>
-      </c>
-      <c r="J4" s="11">
-        <v>1</v>
+        <v>107329.55</v>
+      </c>
+      <c r="J4" s="100">
+        <v>6</v>
       </c>
       <c r="K4" s="12">
         <f>I4/SUM($I$4:$I$10)</f>
@@ -16640,10 +16640,10 @@
         <v>166</v>
       </c>
       <c r="C5" s="5">
-        <v>7478</v>
-      </c>
-      <c r="D5" s="16">
-        <v>3</v>
+        <v>6895</v>
+      </c>
+      <c r="D5" s="22">
+        <v>5</v>
       </c>
       <c r="E5" s="7">
         <f>C5/SUM($C$4:$C$10)</f>
@@ -16658,13 +16658,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="9">
-        <v>16.86856479584869</v>
+        <v>16.9011994669036</v>
       </c>
       <c r="I5" s="10">
-        <v>123528.5</v>
-      </c>
-      <c r="J5" s="100">
-        <v>2</v>
+        <v>114133.8</v>
+      </c>
+      <c r="J5" s="25">
+        <v>5</v>
       </c>
       <c r="K5" s="12">
         <f>I5/SUM($I$4:$I$10)</f>
@@ -16687,10 +16687,10 @@
         <v>167</v>
       </c>
       <c r="C6" s="5">
-        <v>7493</v>
-      </c>
-      <c r="D6" s="50">
-        <v>2</v>
+        <v>6946</v>
+      </c>
+      <c r="D6" s="44">
+        <v>4</v>
       </c>
       <c r="E6" s="7">
         <f>C6/SUM($C$4:$C$10)</f>
@@ -16705,13 +16705,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="9">
-        <v>16.74811692726037</v>
+        <v>16.83219067235545</v>
       </c>
       <c r="I6" s="10">
-        <v>123182.4</v>
-      </c>
-      <c r="J6" s="19">
-        <v>3</v>
+        <v>114408.4</v>
+      </c>
+      <c r="J6" s="45">
+        <v>4</v>
       </c>
       <c r="K6" s="12">
         <f>I6/SUM($I$4:$I$10)</f>
@@ -16734,10 +16734,10 @@
         <v>168</v>
       </c>
       <c r="C7" s="5">
-        <v>6946</v>
-      </c>
-      <c r="D7" s="44">
-        <v>4</v>
+        <v>7478</v>
+      </c>
+      <c r="D7" s="16">
+        <v>3</v>
       </c>
       <c r="E7" s="7">
         <f>C7/SUM($C$4:$C$10)</f>
@@ -16752,13 +16752,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="9">
-        <v>16.83219067235545</v>
+        <v>16.86856479584869</v>
       </c>
       <c r="I7" s="10">
-        <v>114408.4</v>
-      </c>
-      <c r="J7" s="45">
-        <v>4</v>
+        <v>123528.5</v>
+      </c>
+      <c r="J7" s="101">
+        <v>2</v>
       </c>
       <c r="K7" s="12">
         <f>I7/SUM($I$4:$I$10)</f>
@@ -16781,10 +16781,10 @@
         <v>169</v>
       </c>
       <c r="C8" s="5">
-        <v>6895</v>
-      </c>
-      <c r="D8" s="22">
-        <v>5</v>
+        <v>8242</v>
+      </c>
+      <c r="D8" s="20">
+        <v>1</v>
       </c>
       <c r="E8" s="7">
         <f>C8/SUM($C$4:$C$10)</f>
@@ -16799,13 +16799,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="9">
-        <v>16.9011994669036</v>
+        <v>16.78681223784851</v>
       </c>
       <c r="I8" s="10">
-        <v>114133.8</v>
-      </c>
-      <c r="J8" s="25">
-        <v>5</v>
+        <v>136073.9</v>
+      </c>
+      <c r="J8" s="11">
+        <v>1</v>
       </c>
       <c r="K8" s="12">
         <f>I8/SUM($I$4:$I$10)</f>
@@ -16828,10 +16828,10 @@
         <v>170</v>
       </c>
       <c r="C9" s="5">
-        <v>6485</v>
-      </c>
-      <c r="D9" s="51">
-        <v>6</v>
+        <v>7493</v>
+      </c>
+      <c r="D9" s="50">
+        <v>2</v>
       </c>
       <c r="E9" s="7">
         <f>C9/SUM($C$4:$C$10)</f>
@@ -16846,13 +16846,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="9">
-        <v>16.85186842518449</v>
+        <v>16.74811692726037</v>
       </c>
       <c r="I9" s="10">
-        <v>107329.55</v>
-      </c>
-      <c r="J9" s="101">
-        <v>6</v>
+        <v>123182.4</v>
+      </c>
+      <c r="J9" s="19">
+        <v>3</v>
       </c>
       <c r="K9" s="12">
         <f>I9/SUM($I$4:$I$10)</f>
